--- a/04_DESIGN_TABLES/DesignTable_5505.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_5505.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,6 +494,16 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>PORTDEPTH@BORE</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -655,7 +665,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Air-Way s155 only (double-pass 9 rows)</t>
+          <t>Air-Way s155 only (double-pass 9 rows) | PORTDEPTH 0.56 = Brennan port depth -04 = 0.560 on 2502-06-04-FG, 5405-04-04, 5406-08-04, 5502-04-04-FG STEPs (tools/_out/genfeat_20261018/angled/scripts/brennan_port_depths_out.txt) - Q-ANGLED-P1 settled from the Brennan STEPs 2026-10-18 (PROPOSAL, genfeat ANGLED)</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -667,6 +677,9 @@
         <is>
           <t>5505-04-04-FG</t>
         </is>
+      </c>
+      <c r="P5" t="n">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1208,24 +1221,50 @@
           <t>5505-20-20-FG</t>
         </is>
       </c>
+      <c r="B17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.66</v>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>5505-20-20-FG</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 (A (1) NPTF) x 1 1/4-11 1/2 (A (2) NPTF)</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1236,6 +1275,11 @@
       <c r="O17" t="inlineStr">
         <is>
           <t>5505-20-20-FG</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>

--- a/04_DESIGN_TABLES/DesignTable_5505.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_5505.xlsx
@@ -1110,24 +1110,50 @@
           <t>5505-08-08-FG</t>
         </is>
       </c>
+      <c r="B14" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.84</v>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>5505-08-08-FG</t>
         </is>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>1/2-14 (A (1) NPTF) x 1/2-14 (A (2) NPTF)</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5505-08-08 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-21] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5505-08-08 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-21 (batch 19 C, staged): Brennan allowed (user 2026-10-18 "yes use brennan but still differentiate"); Air-Way prints no value for this part number, OMi's website file gives no dimension; sizes from the Brennan TFA catalog, each checked on the part's OWN Brennan STEP (09_STEP_FILES/BRENNAN_5505-08-08-FG.stp, every value equal to the catalog within 0.005); end details from the end library: N2_1@DRIVE: Brennan TFA catalog p.32 table TFA-p032-t03 "5505-FG FP-FP 45 DEG ELBOW" row 5505-08-08-FG col "N LGTH" = "0.940" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 716.1, page verified True) [Brennan = yes 2026-10-18] - A1 female port leg: crossing to the port face; own STEP: port face 0.94 (C_ownstep/measure/5505-08-08-FG.txt (forged.py NPTFF legs at 45 / 180 deg)); N2_2@DRIVE: Brennan TFA catalog p.32 table TFA-p032-t03 "5505-FG FP-FP 45 DEG ELBOW" row 5505-08-08-FG col "N1 LGTH" = "0.940" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 716.1, page verified True) [Brennan = yes 2026-10-18] - A2 female port leg: crossing to the port face; own STEP: port face 0.94 (C_ownstep/measure/5505-08-08-FG.txt (forged.py NPTFF legs at 45 / 180 deg)); W@HEX: Brennan TFA catalog p.32 table TFA-p032-t03 "5505-FG FP-FP 45 DEG ELBOW" row 5505-08-08-FG col "Y FLATS" = "1.062" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 716.1, page verified True) [Brennan = yes 2026-10-18] - forged body flats; own STEP: A/F 1.062 on both legs (C_ownstep/measure/5505-08-08-FG.txt (forged.py NPTFF legs at 45 / 180 deg)); TAPDRILL1@BORE: end library: tap drill of the -08 female NPTF port = 0.7 (gen_straight2 FPT[8] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A, row 2405-08-08) [Q-TRANSFER-ENDLIB yes 2026-10-08: new masters take tap drills from the end library] (own STEP: Brennan port drill 0.718); TAPDRILL2@BORE: end library: tap drill of the -08 female NPTF port = 0.7 (gen_straight2 FPT[8] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A, row 2405-08-08) [Q-TRANSFER-ENDLIB yes 2026-10-08: new masters take tap drills from the end library] (own STEP: Brennan port drill 0.718); THDMAJ_A1@DRIVE: end library: pipe OD of the -08 NPTF thread = 0.84 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[8], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A2@DRIVE: end library: pipe OD of the -08 NPTF thread = 0.84 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[8], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; PORTDEPTH@BORE: Brennan port depth -08 = 0.750 measured on this part's own STEP 09_STEP_FILES/BRENNAN_5505-08-08-FG.stp (forged.py: taper depth from the face 0.75 on both ports, mouth 0.049; brennan_port_depths.run 0.7500; C_ownstep/measure/5505-08-08-FG.txt) = the -08 value of gen_tee ANGLED_P1_NOTE (Q-ANGLED-P1, settled from the Brennan STEPs 2026-10-18: the MS51503 P1 0.90 does not fit the 0.94 leg of the 45 deg elbow)</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5505-08-08 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5505-08-08 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-21 batch 19 C (staged, not shipped): filled from the Brennan TFA catalog, checked on the own STEP (tools/_out/batch19_20261021/C_ownstep/measure); marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate). Cross-check only: Air-Way 5505-8-8 (plain): N2 0.94 / 0.94 W 1.13 TAPDRILL 0.70 (legs agree; flats differ: forged 1.062)</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1138,6 +1164,14 @@
       <c r="O14" t="inlineStr">
         <is>
           <t>5505-08-08-FG</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
